--- a/data-manipulation-scripts/sheets-cleanup/sheets/ROLAMENTO - 27_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ROLAMENTO - 27_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>7899258702377</t>
+  </si>
+  <si>
+    <t>ROLAMENTO NACHI 6203 320895</t>
   </si>
   <si>
     <t>7898520247998</t>
@@ -616,8 +619,8 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
-        <v>45.0</v>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C2" s="2">
         <v>36.0</v>
@@ -628,10 +631,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2">
         <v>30.0</v>
@@ -642,10 +645,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2">
         <v>5.0</v>
@@ -656,10 +659,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>5.0</v>
@@ -670,13 +673,13 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2">
-        <v>4.0</v>
+        <v>44.0</v>
       </c>
       <c r="D6" s="2">
         <v>18.0</v>
@@ -685,7 +688,7 @@
     <row r="7">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2">
         <v>3.0</v>
@@ -696,10 +699,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2">
         <v>1.0</v>
@@ -715,476 +718,468 @@
       <c r="D9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2">
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2">
         <v>11.0</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>35.0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>20.0</v>
-      </c>
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C13" s="2">
-        <v>5.0</v>
+        <v>21.0</v>
       </c>
       <c r="D13" s="2">
-        <v>28.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C14" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D14" s="2">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="C15" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2">
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2">
         <v>20.0</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D17" s="2">
         <v>35.0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="D18" s="2">
-        <v>30.0</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C19" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="D19" s="2">
-        <v>37.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C20" s="2">
         <v>5.0</v>
       </c>
       <c r="D20" s="2">
+        <v>37.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="D21" s="2">
         <v>30.0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>18.0</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="2">
+      <c r="B25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2">
         <v>10.0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D25" s="2">
         <v>18.0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="D26" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C27" s="2">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="D27" s="2">
         <v>35.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2">
-        <v>7.899248112711E12</v>
+      <c r="A28" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2">
         <v>2.0</v>
       </c>
       <c r="D28" s="2">
-        <v>18.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2">
+        <v>7.899248112711E12</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C29" s="2">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="D29" s="2">
         <v>18.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="A30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="D31" s="2">
-        <v>20.0</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C32" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D32" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C33" s="2">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D33" s="2">
-        <v>18.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3"/>
       <c r="B35" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="4"/>
+      <c r="C35" s="2">
+        <v>2.0</v>
+      </c>
       <c r="D35" s="2">
         <v>40.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
+      <c r="B36" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="D36" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D37" s="2">
-        <v>100.0</v>
-      </c>
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="2">
+      <c r="B39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="2">
         <v>1.0</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D39" s="2">
         <v>45.0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-    </row>
     <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="2">
+      <c r="B41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="2">
         <v>17.0</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D41" s="2">
         <v>20.0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-    </row>
     <row r="42">
-      <c r="A42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>18.0</v>
-      </c>
+      <c r="A42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C43" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D43" s="2">
-        <v>35.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C44" s="2">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="D44" s="2">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C45" s="2">
-        <v>24.0</v>
+        <v>14.0</v>
       </c>
       <c r="D45" s="2">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="C46" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="D46" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="D47" s="2">
-        <v>20.0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="C48" s="2">
         <v>5.0</v>
       </c>
       <c r="D48" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="C49" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D49" s="2">
         <v>18.0</v>
@@ -1192,115 +1187,115 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="D50" s="2">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="2">
+      <c r="B51" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" s="2">
         <v>1.0</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D51" s="2">
         <v>35.0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-    </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="D53" s="2">
-        <v>20.0</v>
-      </c>
+      <c r="A53" s="3"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="D54" s="2">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C54" s="2">
+      <c r="B55" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="2">
         <v>1.0</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D55" s="2">
         <v>40.0</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-    </row>
     <row r="56">
-      <c r="A56" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D57" s="2">
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="2">
+      <c r="B58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="2">
         <v>15.0</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D58" s="2">
         <v>30.0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="4"/>
-    </row>
     <row r="59">
-      <c r="A59" s="2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
         <v>7.034117913E10</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="2">
+      <c r="B60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="2">
         <v>4.0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" s="2">
-        <v>3.0</v>
       </c>
       <c r="D60" s="2">
         <v>20.0</v>
@@ -1308,108 +1303,108 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D61" s="2">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="2">
+      <c r="B62" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="2">
         <v>30.0</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D62" s="2">
         <v>25.0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-    </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="2">
+      <c r="B64" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" s="2">
         <v>1.0</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D64" s="2">
         <v>48.0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-    </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B65" s="2" t="s">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="2">
+      <c r="B66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C66" s="2">
         <v>10.0</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D66" s="2">
         <v>35.0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-    </row>
     <row r="67">
-      <c r="A67" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C67" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D67" s="2">
-        <v>78.0</v>
-      </c>
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="C68" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D68" s="2">
+        <v>78.0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D69" s="2">
-        <v>115.0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="C70" s="2">
         <v>2.0</v>
@@ -1419,51 +1414,51 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
+      <c r="A71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C71" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D71" s="2">
+        <v>115.0</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="A72" s="3"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="2">
+      <c r="B73" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" s="2">
         <v>3.0</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D73" s="2">
         <v>125.0</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-    </row>
     <row r="74">
-      <c r="A74" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D74" s="2">
-        <v>160.0</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="C75" s="2">
         <v>1.0</v>
@@ -1473,10 +1468,18 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
+      <c r="A76" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D76" s="2">
+        <v>160.0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3"/>
@@ -7070,14 +7073,20 @@
       <c r="C1008" s="4"/>
       <c r="D1008" s="4"/>
     </row>
+    <row r="1009">
+      <c r="A1009" s="3"/>
+      <c r="B1009" s="4"/>
+      <c r="C1009" s="4"/>
+      <c r="D1009" s="4"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1008">
+  <conditionalFormatting sqref="A1:A1009">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A27 A29:A50 A52:A57 A60:A1008">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A28 A30:A51 A53:A58 A61:A1009">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
